--- a/salidas/empresas/KO.xlsx
+++ b/salidas/empresas/KO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.04666805267334</v>
+        <v>11.04667091369629</v>
       </c>
       <c r="C2" t="n">
         <v>20.69000053405762</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>11.20417308807373</v>
+        <v>11.2041711807251</v>
       </c>
       <c r="C3" t="n">
         <v>20.98500061035156</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.2590799331665</v>
+        <v>11.25907897949219</v>
       </c>
       <c r="C4" t="n">
         <v>20.93499946594238</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.28328800201416</v>
+        <v>11.28328227996826</v>
       </c>
       <c r="C5" t="n">
         <v>20.97999954223633</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83992004394531</v>
+        <v>11.83992099761963</v>
       </c>
       <c r="C6" t="n">
         <v>22.01499938964844</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.65172863006592</v>
+        <v>11.65172290802002</v>
       </c>
       <c r="C7" t="n">
         <v>21.51000022888184</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.05256748199463</v>
+        <v>12.05257034301758</v>
       </c>
       <c r="C8" t="n">
         <v>22.25</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.13653182983398</v>
+        <v>12.13653373718262</v>
       </c>
       <c r="C9" t="n">
         <v>22.40500068664551</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.18568706512451</v>
+        <v>12.18568420410156</v>
       </c>
       <c r="C10" t="n">
         <v>22.34000015258789</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>12.74205207824707</v>
+        <v>12.7420597076416</v>
       </c>
       <c r="C11" t="n">
         <v>23.36000061035156</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.85744857788086</v>
+        <v>12.85744571685791</v>
       </c>
       <c r="C12" t="n">
         <v>23.41500091552734</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.247314453125</v>
+        <v>13.24730491638184</v>
       </c>
       <c r="C13" t="n">
         <v>24.125</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.14572525024414</v>
+        <v>13.14572811126709</v>
       </c>
       <c r="C14" t="n">
         <v>23.94000053405762</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>12.81625652313232</v>
+        <v>12.81625843048096</v>
       </c>
       <c r="C15" t="n">
         <v>23.34000015258789</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.27279186248779</v>
+        <v>13.27278709411621</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.43138790130615</v>
+        <v>14.43139553070068</v>
       </c>
       <c r="C17" t="n">
         <v>26.09499931335449</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.6526050567627</v>
+        <v>14.6525993347168</v>
       </c>
       <c r="C18" t="n">
         <v>26.4950008392334</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.56138610839844</v>
+        <v>14.56138229370117</v>
       </c>
       <c r="C19" t="n">
         <v>26.15500068664551</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.50571060180664</v>
+        <v>14.50570869445801</v>
       </c>
       <c r="C20" t="n">
         <v>26.05500030517578</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.97058010101318</v>
+        <v>14.97058296203613</v>
       </c>
       <c r="C21" t="n">
         <v>26.88999938964844</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.09608459472656</v>
+        <v>16.09607887268066</v>
       </c>
       <c r="C22" t="n">
         <v>28.73500061035156</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.29761505126953</v>
+        <v>17.2976131439209</v>
       </c>
       <c r="C23" t="n">
         <v>30.8799991607666</v>
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.28167724609375</v>
+        <v>17.28168296813965</v>
       </c>
       <c r="C25" t="n">
         <v>30.68499946594238</v>
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.25111770629883</v>
+        <v>17.25110816955566</v>
       </c>
       <c r="C28" t="n">
         <v>30.43499946594238</v>
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.2280101776123</v>
+        <v>16.22800445556641</v>
       </c>
       <c r="C30" t="n">
         <v>28.6299991607666</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.8287410736084</v>
+        <v>14.82874584197998</v>
       </c>
       <c r="C31" t="n">
         <v>25.98999977111816</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>14.69180774688721</v>
+        <v>14.69180488586426</v>
       </c>
       <c r="C32" t="n">
         <v>25.75</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>14.85441493988037</v>
+        <v>14.85442161560059</v>
       </c>
       <c r="C33" t="n">
         <v>26.03499984741211</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.19278049468994</v>
+        <v>15.19278812408447</v>
       </c>
       <c r="C34" t="n">
         <v>26.44000053405762</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>12.65874004364014</v>
+        <v>12.65873527526855</v>
       </c>
       <c r="C35" t="n">
         <v>22.03000068664551</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>13.58057308197021</v>
+        <v>13.58056926727295</v>
       </c>
       <c r="C36" t="n">
         <v>23.43499946594238</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.11697292327881</v>
+        <v>13.11697196960449</v>
       </c>
       <c r="C37" t="n">
         <v>22.63500022888184</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.3781099319458</v>
+        <v>12.37810802459717</v>
       </c>
       <c r="C38" t="n">
         <v>21.36000061035156</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>11.83628082275391</v>
+        <v>11.83627700805664</v>
       </c>
       <c r="C39" t="n">
         <v>20.42499923706055</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.86923885345459</v>
+        <v>12.86923694610596</v>
       </c>
       <c r="C40" t="n">
         <v>21.97500038146973</v>
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.39480876922607</v>
+        <v>14.39480209350586</v>
       </c>
       <c r="C42" t="n">
         <v>24.57999992370605</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.17224884033203</v>
+        <v>14.17224025726318</v>
       </c>
       <c r="C43" t="n">
         <v>23.9950008392334</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>14.40259075164795</v>
+        <v>14.40259456634521</v>
       </c>
       <c r="C45" t="n">
         <v>24.38500022888184</v>
@@ -1330,11 +1342,11 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.98809719085693</v>
+        <v>15.98810482025146</v>
       </c>
       <c r="C46" t="n">
         <v>26.85000038146973</v>
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>15.87198543548584</v>
+        <v>15.87198829650879</v>
       </c>
       <c r="C47" t="n">
         <v>26.65500068664551</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.15117263793945</v>
+        <v>17.15116882324219</v>
       </c>
       <c r="C48" t="n">
         <v>28.60000038146973</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.09120178222656</v>
+        <v>17.09120750427246</v>
       </c>
       <c r="C49" t="n">
         <v>28.5</v>
@@ -1430,7 +1442,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1455,11 +1467,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.8078556060791</v>
+        <v>15.80786037445068</v>
       </c>
       <c r="C51" t="n">
         <v>26.36000061035156</v>
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>16.62648963928223</v>
+        <v>16.62648582458496</v>
       </c>
       <c r="C52" t="n">
         <v>27.5</v>
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>15.53820323944092</v>
+        <v>15.53820419311523</v>
       </c>
       <c r="C54" t="n">
         <v>25.70000076293945</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>15.27943420410156</v>
+        <v>15.2794361114502</v>
       </c>
       <c r="C55" t="n">
         <v>25.05999946594238</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>16.80067825317383</v>
+        <v>16.80066680908203</v>
       </c>
       <c r="C56" t="n">
         <v>27.55500030517578</v>
@@ -1605,11 +1617,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.0354175567627</v>
+        <v>17.03542137145996</v>
       </c>
       <c r="C57" t="n">
         <v>27.94000053405762</v>
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.97538757324219</v>
+        <v>17.97538948059082</v>
       </c>
       <c r="C58" t="n">
         <v>29.26000022888184</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>18.83545875549316</v>
+        <v>18.8354663848877</v>
       </c>
       <c r="C59" t="n">
         <v>30.65999984741211</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.53780174255371</v>
+        <v>19.53780937194824</v>
       </c>
       <c r="C60" t="n">
         <v>31.58499908447266</v>
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.34195899963379</v>
+        <v>20.34196472167969</v>
       </c>
       <c r="C61" t="n">
         <v>32.8849983215332</v>
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.43883323669434</v>
+        <v>19.4388370513916</v>
       </c>
       <c r="C62" t="n">
         <v>31.42499923706055</v>
@@ -1755,7 +1767,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>20.66702651977539</v>
+        <v>20.66703224182129</v>
       </c>
       <c r="C64" t="n">
         <v>33.16999816894531</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>21.01594734191895</v>
+        <v>21.01595115661621</v>
       </c>
       <c r="C65" t="n">
         <v>33.72999954223633</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>20.81344604492188</v>
+        <v>20.81345176696777</v>
       </c>
       <c r="C66" t="n">
         <v>33.40499877929688</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>21.11474990844727</v>
+        <v>21.11475372314453</v>
       </c>
       <c r="C67" t="n">
         <v>33.64500045776367</v>
@@ -1900,11 +1912,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.3406810760498</v>
+        <v>21.34067726135254</v>
       </c>
       <c r="C68" t="n">
         <v>34.00500106811523</v>
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>22.10631561279297</v>
+        <v>22.10631370544434</v>
       </c>
       <c r="C69" t="n">
         <v>35.22499847412109</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>21.34406280517578</v>
+        <v>21.34406661987305</v>
       </c>
       <c r="C70" t="n">
         <v>33.77999877929688</v>
@@ -1987,7 +1999,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2016,11 +2028,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>21.39410591125488</v>
+        <v>21.39410209655762</v>
       </c>
       <c r="C72" t="n">
         <v>33.6150016784668</v>
@@ -2045,7 +2057,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2074,11 +2086,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>21.48957443237305</v>
+        <v>21.48957061767578</v>
       </c>
       <c r="C74" t="n">
         <v>33.76499938964844</v>
@@ -2103,7 +2115,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2132,11 +2144,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>23.7241325378418</v>
+        <v>23.72413063049316</v>
       </c>
       <c r="C76" t="n">
         <v>37.00500106811523</v>
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>24.46460914611816</v>
+        <v>24.46461296081543</v>
       </c>
       <c r="C77" t="n">
         <v>38.15999984741211</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.95492935180664</v>
+        <v>23.95492553710938</v>
       </c>
       <c r="C78" t="n">
         <v>37.3650016784668</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.23519134521484</v>
+        <v>25.23517990112305</v>
       </c>
       <c r="C79" t="n">
         <v>39.09500122070312</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.07753753662109</v>
+        <v>26.07753372192383</v>
       </c>
       <c r="C80" t="n">
         <v>40.40000152587891</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>24.14108848571777</v>
+        <v>24.14109230041504</v>
       </c>
       <c r="C81" t="n">
         <v>37.40000152587891</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.64961624145508</v>
+        <v>24.64961051940918</v>
       </c>
       <c r="C82" t="n">
         <v>37.93000030517578</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>24.16220474243164</v>
+        <v>24.1622142791748</v>
       </c>
       <c r="C83" t="n">
         <v>37.18000030517578</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>24.81219863891602</v>
+        <v>24.81219482421875</v>
       </c>
       <c r="C84" t="n">
         <v>37.91999816894531</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>23.7194709777832</v>
+        <v>23.71946144104004</v>
       </c>
       <c r="C85" t="n">
         <v>36.25</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.36726188659668</v>
+        <v>24.36725234985352</v>
       </c>
       <c r="C86" t="n">
         <v>37.2400016784668</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.33565902709961</v>
+        <v>25.33566856384277</v>
       </c>
       <c r="C87" t="n">
         <v>38.72000122070312</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.65265846252441</v>
+        <v>26.65266036987305</v>
       </c>
       <c r="C88" t="n">
         <v>40.43999862670898</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>27.89830017089844</v>
+        <v>27.89829063415527</v>
       </c>
       <c r="C89" t="n">
         <v>42.33000183105469</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>26.3560905456543</v>
+        <v>26.35608100891113</v>
       </c>
       <c r="C90" t="n">
         <v>39.9900016784668</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.61789131164551</v>
+        <v>26.61787796020508</v>
       </c>
       <c r="C91" t="n">
         <v>40.11000061035156</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>26.59797477722168</v>
+        <v>26.59797096252441</v>
       </c>
       <c r="C92" t="n">
         <v>40.08000183105469</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>25.33709716796875</v>
+        <v>25.33710098266602</v>
       </c>
       <c r="C93" t="n">
         <v>38.18000030517578</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>25.32083702087402</v>
+        <v>25.32083129882812</v>
       </c>
       <c r="C94" t="n">
         <v>37.88000106811523</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>26.45051002502441</v>
+        <v>26.45050811767578</v>
       </c>
       <c r="C95" t="n">
         <v>39.56999969482422</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>27.05313873291016</v>
+        <v>27.05315017700195</v>
       </c>
       <c r="C96" t="n">
         <v>40.18999862670898</v>
@@ -2741,11 +2753,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>27.80705451965332</v>
+        <v>27.80704879760742</v>
       </c>
       <c r="C97" t="n">
         <v>41.31000137329102</v>
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>25.45782470703125</v>
+        <v>25.45782661437988</v>
       </c>
       <c r="C98" t="n">
         <v>37.81999969482422</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>25.71361541748047</v>
+        <v>25.71361351013184</v>
       </c>
       <c r="C99" t="n">
         <v>38.20000076293945</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>26.22943687438965</v>
+        <v>26.22943305969238</v>
       </c>
       <c r="C100" t="n">
         <v>38.65999984741211</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>27.67456817626953</v>
+        <v>27.67456245422363</v>
       </c>
       <c r="C101" t="n">
         <v>40.79000091552734</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>27.75597190856934</v>
+        <v>27.75597953796387</v>
       </c>
       <c r="C102" t="n">
         <v>40.90999984741211</v>
@@ -2915,7 +2927,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>26.85735702514648</v>
+        <v>26.85735321044922</v>
       </c>
       <c r="C104" t="n">
         <v>39.29000091552734</v>
@@ -2973,11 +2985,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>28.51842308044434</v>
+        <v>28.51841163635254</v>
       </c>
       <c r="C105" t="n">
         <v>41.72000122070312</v>
@@ -3002,11 +3014,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.37342071533203</v>
+        <v>29.3734130859375</v>
       </c>
       <c r="C106" t="n">
         <v>42.65999984741211</v>
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.83634757995605</v>
+        <v>28.83635711669922</v>
       </c>
       <c r="C107" t="n">
         <v>41.88000106811523</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>31.08091926574707</v>
+        <v>31.08093070983887</v>
       </c>
       <c r="C108" t="n">
         <v>44.83000183105469</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>29.27139091491699</v>
+        <v>29.27138710021973</v>
       </c>
       <c r="C109" t="n">
         <v>42.22000122070312</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>28.54342269897461</v>
+        <v>28.54341888427734</v>
       </c>
       <c r="C110" t="n">
         <v>41.16999816894531</v>
@@ -3147,7 +3159,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>28.34684562683105</v>
+        <v>28.34684944152832</v>
       </c>
       <c r="C112" t="n">
         <v>40.54999923706055</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>28.35384750366211</v>
+        <v>28.35384559631348</v>
       </c>
       <c r="C113" t="n">
         <v>40.56000137329102</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.63345909118652</v>
+        <v>28.63346862792969</v>
       </c>
       <c r="C114" t="n">
         <v>40.95999908447266</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>27.65035057067871</v>
+        <v>27.65034294128418</v>
       </c>
       <c r="C115" t="n">
         <v>39.22999954223633</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>28.95426368713379</v>
+        <v>28.95427513122559</v>
       </c>
       <c r="C116" t="n">
         <v>41.08000183105469</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>27.71377944946289</v>
+        <v>27.71376609802246</v>
       </c>
       <c r="C117" t="n">
         <v>39.31999969482422</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.52262496948242</v>
+        <v>28.52262306213379</v>
       </c>
       <c r="C118" t="n">
         <v>40.11999893188477</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>30.10800933837891</v>
+        <v>30.10799789428711</v>
       </c>
       <c r="C119" t="n">
         <v>42.34999847412109</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>30.53232383728027</v>
+        <v>30.53232955932617</v>
       </c>
       <c r="C120" t="n">
         <v>42.61999893188477</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>30.77589416503906</v>
+        <v>30.7758903503418</v>
       </c>
       <c r="C121" t="n">
         <v>42.95999908447266</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>30.74724578857422</v>
+        <v>30.74724769592285</v>
       </c>
       <c r="C122" t="n">
         <v>42.91999816894531</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>30.89769172668457</v>
+        <v>30.89767646789551</v>
       </c>
       <c r="C123" t="n">
         <v>43.13000106811523</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>33.49227523803711</v>
+        <v>33.49227142333984</v>
       </c>
       <c r="C124" t="n">
         <v>46.38999938964844</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.34432601928711</v>
+        <v>32.34432983398438</v>
       </c>
       <c r="C125" t="n">
         <v>44.79999923706055</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.19994354248047</v>
+        <v>32.19993591308594</v>
       </c>
       <c r="C126" t="n">
         <v>44.59999847412109</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>32.97795104980469</v>
+        <v>32.97794342041016</v>
       </c>
       <c r="C127" t="n">
         <v>45.33000183105469</v>
@@ -3640,7 +3652,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>31.59568786621094</v>
+        <v>31.59569358825684</v>
       </c>
       <c r="C129" t="n">
         <v>43.43000030517578</v>
@@ -3698,11 +3710,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>31.0396842956543</v>
+        <v>31.0396900177002</v>
       </c>
       <c r="C130" t="n">
         <v>42.31999969482422</v>
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>31.09836959838867</v>
+        <v>31.09836387634277</v>
       </c>
       <c r="C131" t="n">
         <v>42.40000152587891</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>29.8449821472168</v>
+        <v>29.84498023986816</v>
       </c>
       <c r="C132" t="n">
         <v>40.34999847412109</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>30.66599464416504</v>
+        <v>30.6659984588623</v>
       </c>
       <c r="C133" t="n">
         <v>41.45999908447266</v>
@@ -3814,11 +3826,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>30.74736213684082</v>
+        <v>30.74736404418945</v>
       </c>
       <c r="C134" t="n">
         <v>41.56999969482422</v>
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>31.03583145141602</v>
+        <v>31.03582572937012</v>
       </c>
       <c r="C135" t="n">
         <v>41.95999908447266</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>31.66793441772461</v>
+        <v>31.66792106628418</v>
       </c>
       <c r="C136" t="n">
         <v>42.43999862670898</v>
@@ -3901,7 +3913,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3930,7 +3942,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>33.74162292480469</v>
+        <v>33.74164199829102</v>
       </c>
       <c r="C139" t="n">
         <v>44.84999847412109</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>34.4864387512207</v>
+        <v>34.48642349243164</v>
       </c>
       <c r="C140" t="n">
         <v>45.84000015258789</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>34.26825714111328</v>
+        <v>34.26826095581055</v>
       </c>
       <c r="C141" t="n">
         <v>45.54999923706055</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>34.13144302368164</v>
+        <v>34.13145065307617</v>
       </c>
       <c r="C142" t="n">
         <v>45.0099983215332</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>34.86700820922852</v>
+        <v>34.86698913574219</v>
       </c>
       <c r="C143" t="n">
         <v>45.97999954223633</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>34.9923095703125</v>
+        <v>34.99231338500977</v>
       </c>
       <c r="C144" t="n">
         <v>45.77000045776367</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>35.07639694213867</v>
+        <v>35.076416015625</v>
       </c>
       <c r="C145" t="n">
         <v>45.88000106811523</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>36.38375091552734</v>
+        <v>36.38374328613281</v>
       </c>
       <c r="C146" t="n">
         <v>47.59000015258789</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>33.04278182983398</v>
+        <v>33.04277038574219</v>
       </c>
       <c r="C147" t="n">
         <v>43.22000122070312</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>33.49643707275391</v>
+        <v>33.49643325805664</v>
       </c>
       <c r="C148" t="n">
         <v>43.43000030517578</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>33.32673645019531</v>
+        <v>33.32674407958984</v>
       </c>
       <c r="C149" t="n">
         <v>43.20999908447266</v>
@@ -4278,7 +4290,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>34.12935256958008</v>
+        <v>34.12934875488281</v>
       </c>
       <c r="C151" t="n">
         <v>43.86000061035156</v>
@@ -4336,11 +4348,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>36.28480529785156</v>
+        <v>36.28480911254883</v>
       </c>
       <c r="C152" t="n">
         <v>46.63000106811523</v>
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>34.68183135986328</v>
+        <v>34.68183517456055</v>
       </c>
       <c r="C153" t="n">
         <v>44.56999969482422</v>
@@ -4394,11 +4406,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>36.24816131591797</v>
+        <v>36.24813842773438</v>
       </c>
       <c r="C154" t="n">
         <v>46.18999862670898</v>
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>37.57439422607422</v>
+        <v>37.57439804077148</v>
       </c>
       <c r="C155" t="n">
         <v>47.88000106811523</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>39.86475372314453</v>
+        <v>39.86476898193359</v>
       </c>
       <c r="C156" t="n">
         <v>50.40000152587891</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>37.45230484008789</v>
+        <v>37.45229721069336</v>
       </c>
       <c r="C157" t="n">
         <v>47.34999847412109</v>
@@ -4510,11 +4522,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>38.06926727294922</v>
+        <v>38.06925201416016</v>
       </c>
       <c r="C158" t="n">
         <v>48.13000106811523</v>
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>35.86246490478516</v>
+        <v>35.86246109008789</v>
       </c>
       <c r="C159" t="n">
         <v>45.34000015258789</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>37.3882942199707</v>
+        <v>37.3883056640625</v>
       </c>
       <c r="C160" t="n">
         <v>46.86000061035156</v>
@@ -4597,11 +4609,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.14361953735352</v>
+        <v>39.14361572265625</v>
       </c>
       <c r="C161" t="n">
         <v>49.06000137329102</v>
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>39.1994743347168</v>
+        <v>39.199462890625</v>
       </c>
       <c r="C162" t="n">
         <v>49.13000106811523</v>
@@ -4655,11 +4667,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>40.94481658935547</v>
+        <v>40.9448127746582</v>
       </c>
       <c r="C163" t="n">
         <v>50.91999816894531</v>
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>42.31982421875</v>
+        <v>42.31982803344727</v>
       </c>
       <c r="C164" t="n">
         <v>52.63000106811523</v>
@@ -4713,11 +4725,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>44.25771331787109</v>
+        <v>44.25771713256836</v>
       </c>
       <c r="C165" t="n">
         <v>55.04000091552734</v>
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>44.09531402587891</v>
+        <v>44.09530258178711</v>
       </c>
       <c r="C166" t="n">
         <v>54.43999862670898</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>44.08720397949219</v>
+        <v>44.08721542358398</v>
       </c>
       <c r="C167" t="n">
         <v>54.43000030517578</v>
@@ -4800,7 +4812,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4829,11 +4841,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>45.16727447509766</v>
+        <v>45.16726303100586</v>
       </c>
       <c r="C169" t="n">
         <v>55.34999847412109</v>
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>47.65616226196289</v>
+        <v>47.65616607666016</v>
       </c>
       <c r="C170" t="n">
         <v>58.40000152587891</v>
@@ -4887,7 +4899,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>36.42602157592773</v>
+        <v>36.42601776123047</v>
       </c>
       <c r="C172" t="n">
         <v>44.25</v>
@@ -4945,7 +4957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4974,11 +4986,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.42636108398438</v>
+        <v>38.42635726928711</v>
       </c>
       <c r="C174" t="n">
         <v>46.68000030517578</v>
@@ -5003,7 +5015,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>39.24064254760742</v>
+        <v>39.24063491821289</v>
       </c>
       <c r="C176" t="n">
         <v>47.2400016784668</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>41.14285278320312</v>
+        <v>41.14286041259766</v>
       </c>
       <c r="C177" t="n">
         <v>49.52999877929688</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>41.34191513061523</v>
+        <v>41.3419189453125</v>
       </c>
       <c r="C178" t="n">
         <v>49.36999893188477</v>
@@ -5119,11 +5131,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>40.24493789672852</v>
+        <v>40.24493026733398</v>
       </c>
       <c r="C179" t="n">
         <v>48.06000137329102</v>
@@ -5148,7 +5160,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>46.28250885009766</v>
+        <v>46.28250503540039</v>
       </c>
       <c r="C181" t="n">
         <v>54.84000015258789</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>40.63643646240234</v>
+        <v>40.63644409179688</v>
       </c>
       <c r="C182" t="n">
         <v>48.15000152587891</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>41.34536743164062</v>
+        <v>41.34537124633789</v>
       </c>
       <c r="C183" t="n">
         <v>48.9900016784668</v>
@@ -5264,7 +5276,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>45.9359016418457</v>
+        <v>45.93588638305664</v>
       </c>
       <c r="C185" t="n">
         <v>53.97999954223633</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>47.05067443847656</v>
+        <v>47.0506706237793</v>
       </c>
       <c r="C186" t="n">
         <v>55.29000091552734</v>
@@ -5351,7 +5363,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5380,11 +5392,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>48.89706420898438</v>
+        <v>48.89706039428711</v>
       </c>
       <c r="C188" t="n">
         <v>57.02999877929688</v>
@@ -5409,7 +5421,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>45.32688140869141</v>
+        <v>45.32688903808594</v>
       </c>
       <c r="C190" t="n">
         <v>52.47000122070312</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>48.69594573974609</v>
+        <v>48.69594192504883</v>
       </c>
       <c r="C191" t="n">
         <v>56.36999893188477</v>
@@ -5496,11 +5508,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>45.66098022460938</v>
+        <v>45.66097640991211</v>
       </c>
       <c r="C192" t="n">
         <v>52.45000076293945</v>
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>51.54597091674805</v>
+        <v>51.54597854614258</v>
       </c>
       <c r="C193" t="n">
         <v>59.20999908447266</v>
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>53.11298751831055</v>
+        <v>53.11297988891602</v>
       </c>
       <c r="C194" t="n">
         <v>61.0099983215332</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>54.18376922607422</v>
+        <v>54.18377685546875</v>
       </c>
       <c r="C195" t="n">
         <v>62.2400016784668</v>
@@ -5612,11 +5624,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>54.38800811767578</v>
+        <v>54.38801193237305</v>
       </c>
       <c r="C196" t="n">
         <v>62</v>
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>55.59858703613281</v>
+        <v>55.59858322143555</v>
       </c>
       <c r="C198" t="n">
         <v>63.38000106811523</v>
@@ -5699,11 +5711,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>55.58500289916992</v>
+        <v>55.58500671386719</v>
       </c>
       <c r="C199" t="n">
         <v>62.90999984741211</v>
@@ -5728,7 +5740,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5757,7 +5769,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5786,7 +5798,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5815,7 +5827,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>57.0147819519043</v>
+        <v>57.01477813720703</v>
       </c>
       <c r="C204" t="n">
         <v>63.61000061035156</v>
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>57.0147819519043</v>
+        <v>57.01477813720703</v>
       </c>
       <c r="C205" t="n">
         <v>63.61000061035156</v>
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>54.96221160888672</v>
+        <v>54.96220397949219</v>
       </c>
       <c r="C206" t="n">
         <v>61.31999969482422</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>53.33987426757812</v>
+        <v>53.33987808227539</v>
       </c>
       <c r="C207" t="n">
         <v>59.5099983215332</v>
@@ -5960,11 +5972,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>56.02505874633789</v>
+        <v>56.02506256103516</v>
       </c>
       <c r="C208" t="n">
         <v>62.02999877929688</v>
@@ -5989,7 +6001,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6018,11 +6030,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>53.88449859619141</v>
+        <v>53.88449478149414</v>
       </c>
       <c r="C210" t="n">
         <v>59.65999984741211</v>
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>54.80452346801758</v>
+        <v>54.80451965332031</v>
       </c>
       <c r="C211" t="n">
         <v>60.22000122070312</v>
@@ -6076,7 +6088,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6105,11 +6117,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>54.4495849609375</v>
+        <v>54.44958877563477</v>
       </c>
       <c r="C213" t="n">
         <v>59.83000183105469</v>
@@ -6134,7 +6146,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6163,11 +6175,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>51.81783294677734</v>
+        <v>51.81782150268555</v>
       </c>
       <c r="C215" t="n">
         <v>56.4900016784668</v>
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>54.03339004516602</v>
+        <v>54.03338623046875</v>
       </c>
       <c r="C216" t="n">
         <v>58.43999862670898</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>54.48644638061523</v>
+        <v>54.4864387512207</v>
       </c>
       <c r="C217" t="n">
         <v>58.93000030517578</v>
@@ -6250,11 +6262,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>55.00422668457031</v>
+        <v>55.00422286987305</v>
       </c>
       <c r="C218" t="n">
         <v>59.4900016784668</v>
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>55.49425506591797</v>
+        <v>55.4942512512207</v>
       </c>
       <c r="C219" t="n">
         <v>60.02000045776367</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>57.01924514770508</v>
+        <v>57.01924896240234</v>
       </c>
       <c r="C220" t="n">
         <v>61.18000030517578</v>
@@ -6337,11 +6349,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>57.56911849975586</v>
+        <v>57.56912231445312</v>
       </c>
       <c r="C221" t="n">
         <v>61.77000045776367</v>
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,11 +6407,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>59.78155899047852</v>
+        <v>59.78156280517578</v>
       </c>
       <c r="C223" t="n">
         <v>63.65000152587891</v>
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>62.68375778198242</v>
+        <v>62.68375015258789</v>
       </c>
       <c r="C224" t="n">
         <v>66.73999786376953</v>
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>68.06550598144531</v>
+        <v>68.06551361083984</v>
       </c>
       <c r="C225" t="n">
         <v>72.47000122070312</v>
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>67.95529174804688</v>
+        <v>67.95528411865234</v>
       </c>
       <c r="C226" t="n">
         <v>71.86000061035156</v>
@@ -6511,11 +6523,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>61.76119613647461</v>
+        <v>61.76119995117188</v>
       </c>
       <c r="C227" t="n">
         <v>65.30999755859375</v>
@@ -6540,7 +6552,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>59.323486328125</v>
+        <v>59.32349014282227</v>
       </c>
       <c r="C229" t="n">
         <v>62.2599983215332</v>
@@ -6598,7 +6610,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,7 +6668,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>69.20635223388672</v>
+        <v>69.20634460449219</v>
       </c>
       <c r="C234" t="n">
         <v>72.09999847412109</v>
@@ -6743,11 +6755,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>68.39337921142578</v>
+        <v>68.39337158203125</v>
       </c>
       <c r="C235" t="n">
         <v>70.75</v>
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6830,11 +6842,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>64.60261535644531</v>
+        <v>64.60260772705078</v>
       </c>
       <c r="C238" t="n">
         <v>66.31999969482422</v>
@@ -6859,11 +6871,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>67.11580657958984</v>
+        <v>67.11579895019531</v>
       </c>
       <c r="C239" t="n">
         <v>68.90000152587891</v>
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,11 +6958,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
-        <v>73.38459777832031</v>
+        <v>73.38460540771484</v>
       </c>
       <c r="C242" t="n">
         <v>74.80999755859375</v>
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,11 +7045,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>77.79057312011719</v>
+        <v>77.79058074951172</v>
       </c>
       <c r="C245" t="n">
         <v>78.76000213623047</v>
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>88.08999633789062</v>
+        <v>88.09999847412109</v>
       </c>
       <c r="C250" t="n">
-        <v>88.08999633789062</v>
+        <v>88.09999847412109</v>
       </c>
       <c r="D250" t="n">
-        <v>255415800</v>
+        <v>268592100</v>
       </c>
       <c r="E250" t="n">
         <v>3.33</v>
       </c>
       <c r="F250" t="n">
-        <v>26.45345235372091</v>
+        <v>26.45645599823456</v>
       </c>
       <c r="G250" t="n">
         <v>4302482418</v>
       </c>
       <c r="H250" t="n">
-        <v>379005660445.4588</v>
+        <v>379048694460.7328</v>
       </c>
       <c r="I250" t="n">
-        <v>0.05936475159815516</v>
+        <v>0.0624272394179485</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39536</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39626</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39627</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39717</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39906</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39907</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39997</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39998</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40088</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40115</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40270</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7549,13 +7561,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40271</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40361</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7591,13 +7603,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40362</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7633,13 +7645,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40453</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7666,7 +7678,7 @@
       <c r="I10" t="n">
         <v>2.53</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="K10" t="n">
@@ -7679,13 +7691,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40665</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7712,7 +7724,7 @@
       <c r="I11" t="n">
         <v>2.595</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40665</v>
       </c>
       <c r="K11" t="n">
@@ -7725,13 +7737,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40635</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7758,7 +7770,7 @@
       <c r="I12" t="n">
         <v>2.685</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="K12" t="n">
@@ -7771,13 +7783,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40726</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7804,7 +7816,7 @@
       <c r="I13" t="n">
         <v>2.72</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="K13" t="n">
@@ -7817,13 +7829,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7850,7 +7862,7 @@
       <c r="I14" t="n">
         <v>1.845</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="K14" t="n">
@@ -7863,13 +7875,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40998</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7896,7 +7908,7 @@
       <c r="I15" t="n">
         <v>1.88</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K15" t="n">
@@ -7909,13 +7921,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41089</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7942,7 +7954,7 @@
       <c r="I16" t="n">
         <v>1.885</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="K16" t="n">
@@ -7955,13 +7967,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41180</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7988,7 +8000,7 @@
       <c r="I17" t="n">
         <v>1.91</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="K17" t="n">
@@ -8001,13 +8013,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41181</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8034,7 +8046,7 @@
       <c r="I18" t="n">
         <v>1.97</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K18" t="n">
@@ -8047,13 +8059,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41362</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8080,7 +8092,7 @@
       <c r="I19" t="n">
         <v>1.915</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="K19" t="n">
@@ -8093,13 +8105,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41363</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41453</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8126,7 +8138,7 @@
       <c r="I20" t="n">
         <v>1.9</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="K20" t="n">
@@ -8139,13 +8151,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41454</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41544</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8172,7 +8184,7 @@
       <c r="I21" t="n">
         <v>1.94</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="K21" t="n">
@@ -8185,13 +8197,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41545</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8218,7 +8230,7 @@
       <c r="I22" t="n">
         <v>1.9</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="K22" t="n">
@@ -8231,13 +8243,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41726</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8264,7 +8276,7 @@
       <c r="I23" t="n">
         <v>1.87</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="K23" t="n">
@@ -8277,13 +8289,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41727</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41817</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8310,7 +8322,7 @@
       <c r="I24" t="n">
         <v>1.86</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="K24" t="n">
@@ -8323,13 +8335,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41818</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41908</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8356,7 +8368,7 @@
       <c r="I25" t="n">
         <v>1.8</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K25" t="n">
@@ -8369,13 +8381,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41909</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8402,7 +8414,7 @@
       <c r="I26" t="n">
         <v>1.6</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K26" t="n">
@@ -8415,13 +8427,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42097</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8448,7 +8460,7 @@
       <c r="I27" t="n">
         <v>1.59</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="K27" t="n">
@@ -8461,13 +8473,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42098</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42188</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8494,7 +8506,7 @@
       <c r="I28" t="n">
         <v>1.72</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K28" t="n">
@@ -8507,13 +8519,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42189</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42279</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8540,7 +8552,7 @@
       <c r="I29" t="n">
         <v>1.57</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="K29" t="n">
@@ -8553,13 +8565,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42280</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8586,7 +8598,7 @@
       <c r="I30" t="n">
         <v>1.67</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="K30" t="n">
@@ -8599,13 +8611,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8632,7 +8644,7 @@
       <c r="I31" t="n">
         <v>1.66</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="K31" t="n">
@@ -8645,13 +8657,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42462</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8678,7 +8690,7 @@
       <c r="I32" t="n">
         <v>1.74</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K32" t="n">
@@ -8691,13 +8703,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42553</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8724,7 +8736,7 @@
       <c r="I33" t="n">
         <v>1.65</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K33" t="n">
@@ -8737,13 +8749,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8770,7 +8782,7 @@
       <c r="I34" t="n">
         <v>1.49</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="K34" t="n">
@@ -8783,13 +8795,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8816,7 +8828,7 @@
       <c r="I35" t="n">
         <v>1.42</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K35" t="n">
@@ -8829,13 +8841,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8862,7 +8874,7 @@
       <c r="I36" t="n">
         <v>0.95</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K36" t="n">
@@ -8875,13 +8887,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43007</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8908,7 +8920,7 @@
       <c r="I37" t="n">
         <v>1.04</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K37" t="n">
@@ -8921,13 +8933,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8954,7 +8966,7 @@
       <c r="I38" t="n">
         <v>0.2899999999999999</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="K38" t="n">
@@ -8967,13 +8979,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43189</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9000,7 +9012,7 @@
       <c r="I39" t="n">
         <v>0.3399999999999999</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="K39" t="n">
@@ -9013,13 +9025,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43280</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9046,7 +9058,7 @@
       <c r="I40" t="n">
         <v>0.5599999999999999</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K40" t="n">
@@ -9059,13 +9071,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43371</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9092,7 +9104,7 @@
       <c r="I41" t="n">
         <v>0.6699999999999999</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="K41" t="n">
@@ -9105,13 +9117,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43372</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9138,7 +9150,7 @@
       <c r="I42" t="n">
         <v>1.5</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="K42" t="n">
@@ -9151,13 +9163,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43553</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9184,7 +9196,7 @@
       <c r="I43" t="n">
         <v>1.57</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="K43" t="n">
@@ -9197,13 +9209,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43554</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43644</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9230,7 +9242,7 @@
       <c r="I44" t="n">
         <v>1.64</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="K44" t="n">
@@ -9243,13 +9255,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43645</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43735</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9276,7 +9288,7 @@
       <c r="I45" t="n">
         <v>1.8</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="K45" t="n">
@@ -9289,13 +9301,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43736</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9322,7 +9334,7 @@
       <c r="I46" t="n">
         <v>2.07</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="K46" t="n">
@@ -9335,13 +9347,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43917</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9368,7 +9380,7 @@
       <c r="I47" t="n">
         <v>2.319999999999999</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="K47" t="n">
@@ -9381,13 +9393,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43918</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44008</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44034</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9414,7 +9426,7 @@
       <c r="I48" t="n">
         <v>2.12</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44034</v>
       </c>
       <c r="K48" t="n">
@@ -9427,13 +9439,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44009</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44099</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9460,7 +9472,7 @@
       <c r="I49" t="n">
         <v>1.92</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K49" t="n">
@@ -9473,13 +9485,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44100</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9506,7 +9518,7 @@
       <c r="I50" t="n">
         <v>1.79</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="K50" t="n">
@@ -9519,13 +9531,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44288</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9552,7 +9564,7 @@
       <c r="I51" t="n">
         <v>1.67</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="K51" t="n">
@@ -9565,13 +9577,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44289</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44379</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44403</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9598,7 +9610,7 @@
       <c r="I52" t="n">
         <v>1.87</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44403</v>
       </c>
       <c r="K52" t="n">
@@ -9611,13 +9623,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44380</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9644,7 +9656,7 @@
       <c r="I53" t="n">
         <v>2.04</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="K53" t="n">
@@ -9657,13 +9669,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44471</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9690,7 +9702,7 @@
       <c r="I54" t="n">
         <v>2.25</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="K54" t="n">
@@ -9703,13 +9715,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9736,7 +9748,7 @@
       <c r="I55" t="n">
         <v>2.37</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="K55" t="n">
@@ -9749,13 +9761,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44653</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9782,7 +9794,7 @@
       <c r="I56" t="n">
         <v>2.2</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="K56" t="n">
@@ -9795,13 +9807,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44744</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9828,7 +9840,7 @@
       <c r="I57" t="n">
         <v>2.28</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="K57" t="n">
@@ -9841,13 +9853,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9874,7 +9886,7 @@
       <c r="I58" t="n">
         <v>2.19</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="K58" t="n">
@@ -9887,13 +9899,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9920,7 +9932,7 @@
       <c r="I59" t="n">
         <v>2.27</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="K59" t="n">
@@ -9933,13 +9945,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9966,7 +9978,7 @@
       <c r="I60" t="n">
         <v>2.42</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K60" t="n">
@@ -9979,13 +9991,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45198</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10012,7 +10024,7 @@
       <c r="I61" t="n">
         <v>2.48</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="K61" t="n">
@@ -10025,13 +10037,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10058,7 +10070,7 @@
       <c r="I62" t="n">
         <v>2.47</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="K62" t="n">
@@ -10071,13 +10083,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45380</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10104,7 +10116,7 @@
       <c r="I63" t="n">
         <v>2.49</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K63" t="n">
@@ -10117,13 +10129,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45471</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10150,7 +10162,7 @@
       <c r="I64" t="n">
         <v>2.46</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="K64" t="n">
@@ -10163,13 +10175,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45562</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10196,7 +10208,7 @@
       <c r="I65" t="n">
         <v>2.41</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K65" t="n">
@@ -10209,13 +10221,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10242,7 +10254,7 @@
       <c r="I66" t="n">
         <v>2.46</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="K66" t="n">
@@ -10255,13 +10267,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45744</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10288,7 +10300,7 @@
       <c r="I67" t="n">
         <v>2.49</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K67" t="n">
@@ -10301,13 +10313,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45835</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10334,7 +10346,7 @@
       <c r="I68" t="n">
         <v>2.81</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K68" t="n">
@@ -10347,13 +10359,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45926</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10380,7 +10392,7 @@
       <c r="I69" t="n">
         <v>3.01</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K69" t="n">
@@ -10393,13 +10405,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45927</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10426,7 +10438,7 @@
       <c r="I70" t="n">
         <v>3.04</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="K70" t="n">
@@ -10439,13 +10451,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10472,7 +10484,7 @@
       <c r="I71" t="n">
         <v>3.180000000000001</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="K71" t="n">
@@ -10485,13 +10497,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I72" t="n">
         <v>3.33</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46248</v>
       </c>
       <c r="K72" t="n">
@@ -10549,52 +10561,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40018</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40024</v>
       </c>
       <c r="C2" t="n">
@@ -10623,10 +10635,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40231</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40235</v>
       </c>
       <c r="C3" t="n">
@@ -10655,10 +10667,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40294</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40297</v>
       </c>
       <c r="C4" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40385</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40392</v>
       </c>
       <c r="C5" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40476</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40480</v>
       </c>
       <c r="C6" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40596</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="C7" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40659</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40665</v>
       </c>
       <c r="C8" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40750</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40756</v>
       </c>
       <c r="C9" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40840</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C10" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40959</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40962</v>
       </c>
       <c r="C11" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41022</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C12" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41113</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41116</v>
       </c>
       <c r="C13" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41204</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41207</v>
       </c>
       <c r="C14" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41330</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C15" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41386</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41389</v>
       </c>
       <c r="C16" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41477</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41480</v>
       </c>
       <c r="C17" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41568</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41571</v>
       </c>
       <c r="C18" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41694</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41697</v>
       </c>
       <c r="C19" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41750</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41753</v>
       </c>
       <c r="C20" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41845</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41850</v>
       </c>
       <c r="C21" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41936</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C22" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42058</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C23" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42121</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="C24" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42212</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C25" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42303</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42305</v>
       </c>
       <c r="C26" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42422</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42425</v>
       </c>
       <c r="C27" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42485</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42488</v>
       </c>
       <c r="C28" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42576</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C29" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42667</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C30" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42786</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42790</v>
       </c>
       <c r="C31" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42849</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C32" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42940</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C33" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43031</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C34" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43147</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43154</v>
       </c>
       <c r="C35" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43217</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43221</v>
       </c>
       <c r="C36" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43304</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C37" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43399</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43403</v>
       </c>
       <c r="C38" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43511</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43517</v>
       </c>
       <c r="C39" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43577</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43580</v>
       </c>
       <c r="C40" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43668</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43671</v>
       </c>
       <c r="C41" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43759</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43762</v>
       </c>
       <c r="C42" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43880</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43885</v>
       </c>
       <c r="C43" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43942</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43945</v>
       </c>
       <c r="C44" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44034</v>
       </c>
       <c r="C45" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44123</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C46" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44249</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44252</v>
       </c>
       <c r="C47" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44309</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44313</v>
       </c>
       <c r="C48" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44399</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44403</v>
       </c>
       <c r="C49" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44494</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44497</v>
       </c>
       <c r="C50" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44610</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44614</v>
       </c>
       <c r="C51" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44677</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44679</v>
       </c>
       <c r="C52" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44767</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44769</v>
       </c>
       <c r="C53" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44858</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44860</v>
       </c>
       <c r="C54" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44974</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44978</v>
       </c>
       <c r="C55" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45040</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45042</v>
       </c>
       <c r="C56" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45132</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C57" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45219</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45223</v>
       </c>
       <c r="C58" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45338</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45342</v>
       </c>
       <c r="C59" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45412</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C60" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45498</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45502</v>
       </c>
       <c r="C61" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45587</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C62" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45706</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45708</v>
       </c>
       <c r="C63" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45776</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C64" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45860</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C65" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45951</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C66" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46071</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46073</v>
       </c>
       <c r="C67" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46140</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="C68" t="n">
@@ -12753,12 +12765,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/KO.xlsx
+++ b/salidas/empresas/KO.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>11.04667091369629</v>
+        <v>11.04666423797607</v>
       </c>
       <c r="C2" t="n">
         <v>20.69000053405762</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>11.2041711807251</v>
+        <v>11.20417213439941</v>
       </c>
       <c r="C3" t="n">
         <v>20.98500061035156</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>11.25907897949219</v>
+        <v>11.25908374786377</v>
       </c>
       <c r="C4" t="n">
         <v>20.93499946594238</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>11.28328227996826</v>
+        <v>11.28328418731689</v>
       </c>
       <c r="C5" t="n">
         <v>20.97999954223633</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>11.83992099761963</v>
+        <v>11.83991527557373</v>
       </c>
       <c r="C6" t="n">
         <v>22.01499938964844</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>11.65172290802002</v>
+        <v>11.65172004699707</v>
       </c>
       <c r="C7" t="n">
         <v>21.51000022888184</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>12.05257034301758</v>
+        <v>12.05257606506348</v>
       </c>
       <c r="C8" t="n">
         <v>22.25</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>12.13653373718262</v>
+        <v>12.13653564453125</v>
       </c>
       <c r="C9" t="n">
         <v>22.40500068664551</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>12.18568420410156</v>
+        <v>12.18568229675293</v>
       </c>
       <c r="C10" t="n">
         <v>22.34000015258789</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>12.85744571685791</v>
+        <v>12.85744380950928</v>
       </c>
       <c r="C12" t="n">
         <v>23.41500091552734</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>13.24730491638184</v>
+        <v>13.24731540679932</v>
       </c>
       <c r="C13" t="n">
         <v>24.125</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>13.14572811126709</v>
+        <v>13.14572429656982</v>
       </c>
       <c r="C14" t="n">
         <v>23.94000053405762</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>13.27278709411621</v>
+        <v>13.27278614044189</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>14.43139553070068</v>
+        <v>14.4313907623291</v>
       </c>
       <c r="C17" t="n">
         <v>26.09499931335449</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>14.6525993347168</v>
+        <v>14.6526050567627</v>
       </c>
       <c r="C18" t="n">
         <v>26.4950008392334</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>14.56138229370117</v>
+        <v>14.56138610839844</v>
       </c>
       <c r="C19" t="n">
         <v>26.15500068664551</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.50570869445801</v>
+        <v>14.50569820404053</v>
       </c>
       <c r="C20" t="n">
         <v>26.05500030517578</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>14.97058296203613</v>
+        <v>14.97058391571045</v>
       </c>
       <c r="C21" t="n">
         <v>26.88999938964844</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>16.09607887268066</v>
+        <v>16.09608268737793</v>
       </c>
       <c r="C22" t="n">
         <v>28.73500061035156</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>17.2976131439209</v>
+        <v>17.2976188659668</v>
       </c>
       <c r="C23" t="n">
         <v>30.8799991607666</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>17.48724365234375</v>
+        <v>17.48725128173828</v>
       </c>
       <c r="C24" t="n">
         <v>31.04999923706055</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>17.28168296813965</v>
+        <v>17.28166580200195</v>
       </c>
       <c r="C25" t="n">
         <v>30.68499946594238</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>16.61429595947266</v>
+        <v>16.61428833007812</v>
       </c>
       <c r="C26" t="n">
         <v>29.5</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>16.46223068237305</v>
+        <v>16.46222305297852</v>
       </c>
       <c r="C27" t="n">
         <v>29.22999954223633</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>17.25110816955566</v>
+        <v>17.25111198425293</v>
       </c>
       <c r="C28" t="n">
         <v>30.43499946594238</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>16.68429183959961</v>
+        <v>16.68429756164551</v>
       </c>
       <c r="C29" t="n">
         <v>29.43499946594238</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>16.22800445556641</v>
+        <v>16.2280101776123</v>
       </c>
       <c r="C30" t="n">
         <v>28.6299991607666</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.82874584197998</v>
+        <v>14.82874393463135</v>
       </c>
       <c r="C31" t="n">
         <v>25.98999977111816</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>14.85442161560059</v>
+        <v>14.85442447662354</v>
       </c>
       <c r="C33" t="n">
         <v>26.03499984741211</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>15.19278812408447</v>
+        <v>15.19278335571289</v>
       </c>
       <c r="C34" t="n">
         <v>26.44000053405762</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>12.65873527526855</v>
+        <v>12.65873432159424</v>
       </c>
       <c r="C35" t="n">
         <v>22.03000068664551</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>13.58056926727295</v>
+        <v>13.58057022094727</v>
       </c>
       <c r="C36" t="n">
         <v>23.43499946594238</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>13.11697196960449</v>
+        <v>13.11696910858154</v>
       </c>
       <c r="C37" t="n">
         <v>22.63500022888184</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>12.37810802459717</v>
+        <v>12.37810707092285</v>
       </c>
       <c r="C38" t="n">
         <v>21.36000061035156</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>12.86923694610596</v>
+        <v>12.86924457550049</v>
       </c>
       <c r="C40" t="n">
         <v>21.97500038146973</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>14.39480209350586</v>
+        <v>14.39480781555176</v>
       </c>
       <c r="C42" t="n">
         <v>24.57999992370605</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>14.17224025726318</v>
+        <v>14.17224597930908</v>
       </c>
       <c r="C43" t="n">
         <v>23.9950008392334</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>14.71857738494873</v>
+        <v>14.718581199646</v>
       </c>
       <c r="C44" t="n">
         <v>24.92000007629395</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>15.98810482025146</v>
+        <v>15.9881010055542</v>
       </c>
       <c r="C46" t="n">
         <v>26.85000038146973</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>15.87198829650879</v>
+        <v>15.87198352813721</v>
       </c>
       <c r="C47" t="n">
         <v>26.65500068664551</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>17.15116882324219</v>
+        <v>17.15117454528809</v>
       </c>
       <c r="C48" t="n">
         <v>28.60000038146973</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>17.09120750427246</v>
+        <v>17.0911979675293</v>
       </c>
       <c r="C49" t="n">
         <v>28.5</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>16.26662445068359</v>
+        <v>16.26662063598633</v>
       </c>
       <c r="C50" t="n">
         <v>27.125</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>15.80786037445068</v>
+        <v>15.80785465240479</v>
       </c>
       <c r="C51" t="n">
         <v>26.36000061035156</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>16.15792274475098</v>
+        <v>16.15790939331055</v>
       </c>
       <c r="C53" t="n">
         <v>26.72500038146973</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>15.53820419311523</v>
+        <v>15.53820514678955</v>
       </c>
       <c r="C54" t="n">
         <v>25.70000076293945</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>15.2794361114502</v>
+        <v>15.27943325042725</v>
       </c>
       <c r="C55" t="n">
         <v>25.05999946594238</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>16.80066680908203</v>
+        <v>16.80067825317383</v>
       </c>
       <c r="C56" t="n">
         <v>27.55500030517578</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>17.03542137145996</v>
+        <v>17.0354175567627</v>
       </c>
       <c r="C57" t="n">
         <v>27.94000053405762</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>17.97538948059082</v>
+        <v>17.97539138793945</v>
       </c>
       <c r="C58" t="n">
         <v>29.26000022888184</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>18.8354663848877</v>
+        <v>18.83545684814453</v>
       </c>
       <c r="C59" t="n">
         <v>30.65999984741211</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>19.53780937194824</v>
+        <v>19.53781127929688</v>
       </c>
       <c r="C60" t="n">
         <v>31.58499908447266</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>20.34196472167969</v>
+        <v>20.34196090698242</v>
       </c>
       <c r="C61" t="n">
         <v>32.8849983215332</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>19.4388370513916</v>
+        <v>19.4388313293457</v>
       </c>
       <c r="C62" t="n">
         <v>31.42499923706055</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>19.76977348327637</v>
+        <v>19.76977157592773</v>
       </c>
       <c r="C63" t="n">
         <v>31.95999908447266</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>21.01595115661621</v>
+        <v>21.01594924926758</v>
       </c>
       <c r="C65" t="n">
         <v>33.72999954223633</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>21.34067726135254</v>
+        <v>21.3406867980957</v>
       </c>
       <c r="C68" t="n">
         <v>34.00500106811523</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>21.34406661987305</v>
+        <v>21.34406471252441</v>
       </c>
       <c r="C70" t="n">
         <v>33.77999877929688</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>21.58417129516602</v>
+        <v>21.58416557312012</v>
       </c>
       <c r="C71" t="n">
         <v>34.15999984741211</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>21.39410209655762</v>
+        <v>21.39410018920898</v>
       </c>
       <c r="C72" t="n">
         <v>33.6150016784668</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>22.26603317260742</v>
+        <v>22.26604080200195</v>
       </c>
       <c r="C73" t="n">
         <v>34.98500061035156</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>21.48957061767578</v>
+        <v>21.48956871032715</v>
       </c>
       <c r="C74" t="n">
         <v>33.76499938964844</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>22.23102760314941</v>
+        <v>22.23102188110352</v>
       </c>
       <c r="C75" t="n">
         <v>34.93000030517578</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>24.46461296081543</v>
+        <v>24.46460342407227</v>
       </c>
       <c r="C77" t="n">
         <v>38.15999984741211</v>
@@ -2206,7 +2206,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>23.95492553710938</v>
+        <v>23.95493316650391</v>
       </c>
       <c r="C78" t="n">
         <v>37.3650016784668</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>25.23517990112305</v>
+        <v>25.23517608642578</v>
       </c>
       <c r="C79" t="n">
         <v>39.09500122070312</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>26.07753372192383</v>
+        <v>26.07754135131836</v>
       </c>
       <c r="C80" t="n">
         <v>40.40000152587891</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>24.14109230041504</v>
+        <v>24.14108467102051</v>
       </c>
       <c r="C81" t="n">
         <v>37.40000152587891</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>24.64961051940918</v>
+        <v>24.64961814880371</v>
       </c>
       <c r="C82" t="n">
         <v>37.93000030517578</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>24.1622142791748</v>
+        <v>24.1622200012207</v>
       </c>
       <c r="C83" t="n">
         <v>37.18000030517578</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>24.81219482421875</v>
+        <v>24.81219673156738</v>
       </c>
       <c r="C84" t="n">
         <v>37.91999816894531</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>23.71946144104004</v>
+        <v>23.7194766998291</v>
       </c>
       <c r="C85" t="n">
         <v>36.25</v>
@@ -2438,7 +2438,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>24.36725234985352</v>
+        <v>24.36725425720215</v>
       </c>
       <c r="C86" t="n">
         <v>37.2400016784668</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>25.33566856384277</v>
+        <v>25.33566093444824</v>
       </c>
       <c r="C87" t="n">
         <v>38.72000122070312</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>26.65266036987305</v>
+        <v>26.65265846252441</v>
       </c>
       <c r="C88" t="n">
         <v>40.43999862670898</v>
@@ -2525,7 +2525,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>27.89829063415527</v>
+        <v>27.89829254150391</v>
       </c>
       <c r="C89" t="n">
         <v>42.33000183105469</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>26.35608100891113</v>
+        <v>26.35607719421387</v>
       </c>
       <c r="C90" t="n">
         <v>39.9900016784668</v>
@@ -2583,7 +2583,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>26.61787796020508</v>
+        <v>26.61788558959961</v>
       </c>
       <c r="C91" t="n">
         <v>40.11000061035156</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>26.59797096252441</v>
+        <v>26.59797286987305</v>
       </c>
       <c r="C92" t="n">
         <v>40.08000183105469</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>25.33710098266602</v>
+        <v>25.33709716796875</v>
       </c>
       <c r="C93" t="n">
         <v>38.18000030517578</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>25.32083129882812</v>
+        <v>25.32083511352539</v>
       </c>
       <c r="C94" t="n">
         <v>37.88000106811523</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>26.45050811767578</v>
+        <v>26.45050048828125</v>
       </c>
       <c r="C95" t="n">
         <v>39.56999969482422</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>27.05315017700195</v>
+        <v>27.05313301086426</v>
       </c>
       <c r="C96" t="n">
         <v>40.18999862670898</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>27.80704879760742</v>
+        <v>27.80705070495605</v>
       </c>
       <c r="C97" t="n">
         <v>41.31000137329102</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>25.45782661437988</v>
+        <v>25.45781517028809</v>
       </c>
       <c r="C98" t="n">
         <v>37.81999969482422</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>25.71361351013184</v>
+        <v>25.7136116027832</v>
       </c>
       <c r="C99" t="n">
         <v>38.20000076293945</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>26.22943305969238</v>
+        <v>26.22943687438965</v>
       </c>
       <c r="C100" t="n">
         <v>38.65999984741211</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>27.67456245422363</v>
+        <v>27.67456436157227</v>
       </c>
       <c r="C101" t="n">
         <v>40.79000091552734</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>28.95590209960938</v>
+        <v>28.95589637756348</v>
       </c>
       <c r="C103" t="n">
         <v>42.36000061035156</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>26.85735321044922</v>
+        <v>26.85734558105469</v>
       </c>
       <c r="C104" t="n">
         <v>39.29000091552734</v>
@@ -3018,7 +3018,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>29.3734130859375</v>
+        <v>29.37341117858887</v>
       </c>
       <c r="C106" t="n">
         <v>42.65999984741211</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>28.83635711669922</v>
+        <v>28.83634185791016</v>
       </c>
       <c r="C107" t="n">
         <v>41.88000106811523</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>31.08093070983887</v>
+        <v>31.0809211730957</v>
       </c>
       <c r="C108" t="n">
         <v>44.83000183105469</v>
@@ -3105,7 +3105,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>29.27138710021973</v>
+        <v>29.27138519287109</v>
       </c>
       <c r="C109" t="n">
         <v>42.22000122070312</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>28.54341888427734</v>
+        <v>28.54342651367188</v>
       </c>
       <c r="C110" t="n">
         <v>41.16999816894531</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>30.0201587677002</v>
+        <v>30.02016067504883</v>
       </c>
       <c r="C111" t="n">
         <v>43.29999923706055</v>
@@ -3221,7 +3221,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>28.35384559631348</v>
+        <v>28.35383605957031</v>
       </c>
       <c r="C113" t="n">
         <v>40.56000137329102</v>
@@ -3250,7 +3250,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>28.63346862792969</v>
+        <v>28.63345909118652</v>
       </c>
       <c r="C114" t="n">
         <v>40.95999908447266</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>27.65034294128418</v>
+        <v>27.65033340454102</v>
       </c>
       <c r="C115" t="n">
         <v>39.22999954223633</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>28.95427513122559</v>
+        <v>28.95427322387695</v>
       </c>
       <c r="C116" t="n">
         <v>41.08000183105469</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>27.71376609802246</v>
+        <v>27.71377182006836</v>
       </c>
       <c r="C117" t="n">
         <v>39.31999969482422</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>28.52262306213379</v>
+        <v>28.52261924743652</v>
       </c>
       <c r="C118" t="n">
         <v>40.11999893188477</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>30.10799789428711</v>
+        <v>30.10800743103027</v>
       </c>
       <c r="C119" t="n">
         <v>42.34999847412109</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>30.53232955932617</v>
+        <v>30.53232765197754</v>
       </c>
       <c r="C120" t="n">
         <v>42.61999893188477</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>30.7758903503418</v>
+        <v>30.77588653564453</v>
       </c>
       <c r="C121" t="n">
         <v>42.95999908447266</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>30.74724769592285</v>
+        <v>30.74724006652832</v>
       </c>
       <c r="C122" t="n">
         <v>42.91999816894531</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>30.89767646789551</v>
+        <v>30.89769172668457</v>
       </c>
       <c r="C123" t="n">
         <v>43.13000106811523</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>33.49227142333984</v>
+        <v>33.49225997924805</v>
       </c>
       <c r="C124" t="n">
         <v>46.38999938964844</v>
@@ -3569,7 +3569,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>32.34432983398438</v>
+        <v>32.34434127807617</v>
       </c>
       <c r="C125" t="n">
         <v>44.79999923706055</v>
@@ -3598,7 +3598,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>32.19993591308594</v>
+        <v>32.1999397277832</v>
       </c>
       <c r="C126" t="n">
         <v>44.59999847412109</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>32.97794342041016</v>
+        <v>32.97795867919922</v>
       </c>
       <c r="C127" t="n">
         <v>45.33000183105469</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>31.74118614196777</v>
+        <v>31.74117660522461</v>
       </c>
       <c r="C128" t="n">
         <v>43.63000106811523</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>31.59569358825684</v>
+        <v>31.5956859588623</v>
       </c>
       <c r="C129" t="n">
         <v>43.43000030517578</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>31.0396900177002</v>
+        <v>31.0396842956543</v>
       </c>
       <c r="C130" t="n">
         <v>42.31999969482422</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>31.09836387634277</v>
+        <v>31.09836196899414</v>
       </c>
       <c r="C131" t="n">
         <v>42.40000152587891</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>29.84498023986816</v>
+        <v>29.84497451782227</v>
       </c>
       <c r="C132" t="n">
         <v>40.34999847412109</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>30.6659984588623</v>
+        <v>30.66600227355957</v>
       </c>
       <c r="C133" t="n">
         <v>41.45999908447266</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>31.03582572937012</v>
+        <v>31.03582763671875</v>
       </c>
       <c r="C135" t="n">
         <v>41.95999908447266</v>
@@ -3888,7 +3888,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>31.66792106628418</v>
+        <v>31.66792869567871</v>
       </c>
       <c r="C136" t="n">
         <v>42.43999862670898</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>32.19771194458008</v>
+        <v>32.19771575927734</v>
       </c>
       <c r="C137" t="n">
         <v>43.15000152587891</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>33.92885589599609</v>
+        <v>33.92885971069336</v>
       </c>
       <c r="C138" t="n">
         <v>45.47000122070312</v>
@@ -3975,7 +3975,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>33.74164199829102</v>
+        <v>33.74161911010742</v>
       </c>
       <c r="C139" t="n">
         <v>44.84999847412109</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>34.48642349243164</v>
+        <v>34.48643493652344</v>
       </c>
       <c r="C140" t="n">
         <v>45.84000015258789</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>34.26826095581055</v>
+        <v>34.26826477050781</v>
       </c>
       <c r="C141" t="n">
         <v>45.54999923706055</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>34.13145065307617</v>
+        <v>34.13144302368164</v>
       </c>
       <c r="C142" t="n">
         <v>45.0099983215332</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>34.86698913574219</v>
+        <v>34.86700057983398</v>
       </c>
       <c r="C143" t="n">
         <v>45.97999954223633</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>35.076416015625</v>
+        <v>35.0764045715332</v>
       </c>
       <c r="C145" t="n">
         <v>45.88000106811523</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>33.04277038574219</v>
+        <v>33.04277420043945</v>
       </c>
       <c r="C147" t="n">
         <v>43.22000122070312</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>33.32674407958984</v>
+        <v>33.32674789428711</v>
       </c>
       <c r="C149" t="n">
         <v>43.20999908447266</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>33.16477966308594</v>
+        <v>33.16477584838867</v>
       </c>
       <c r="C150" t="n">
         <v>43</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>34.12934875488281</v>
+        <v>34.12934494018555</v>
       </c>
       <c r="C151" t="n">
         <v>43.86000061035156</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>36.28480911254883</v>
+        <v>36.28479766845703</v>
       </c>
       <c r="C152" t="n">
         <v>46.63000106811523</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>34.68183517456055</v>
+        <v>34.68182754516602</v>
       </c>
       <c r="C153" t="n">
         <v>44.56999969482422</v>
@@ -4410,7 +4410,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>36.24813842773438</v>
+        <v>36.24814987182617</v>
       </c>
       <c r="C154" t="n">
         <v>46.18999862670898</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>37.57439804077148</v>
+        <v>37.57439041137695</v>
       </c>
       <c r="C155" t="n">
         <v>47.88000106811523</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>39.86476898193359</v>
+        <v>39.8647575378418</v>
       </c>
       <c r="C156" t="n">
         <v>50.40000152587891</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>37.45229721069336</v>
+        <v>37.45230102539062</v>
       </c>
       <c r="C157" t="n">
         <v>47.34999847412109</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>38.06925201416016</v>
+        <v>38.06926727294922</v>
       </c>
       <c r="C158" t="n">
         <v>48.13000106811523</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>39.14361572265625</v>
+        <v>39.14362335205078</v>
       </c>
       <c r="C161" t="n">
         <v>49.06000137329102</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>39.199462890625</v>
+        <v>39.19946670532227</v>
       </c>
       <c r="C162" t="n">
         <v>49.13000106811523</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>40.9448127746582</v>
+        <v>40.94481658935547</v>
       </c>
       <c r="C163" t="n">
         <v>50.91999816894531</v>
@@ -4700,7 +4700,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>42.31982803344727</v>
+        <v>42.31981658935547</v>
       </c>
       <c r="C164" t="n">
         <v>52.63000106811523</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>44.25771713256836</v>
+        <v>44.25770950317383</v>
       </c>
       <c r="C165" t="n">
         <v>55.04000091552734</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>44.08721542358398</v>
+        <v>44.08720016479492</v>
       </c>
       <c r="C167" t="n">
         <v>54.43000030517578</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>43.57600784301758</v>
+        <v>43.57601165771484</v>
       </c>
       <c r="C168" t="n">
         <v>53.40000152587891</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>45.16726303100586</v>
+        <v>45.16727447509766</v>
       </c>
       <c r="C169" t="n">
         <v>55.34999847412109</v>
@@ -4874,7 +4874,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>47.65616607666016</v>
+        <v>47.65616226196289</v>
       </c>
       <c r="C170" t="n">
         <v>58.40000152587891</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>43.64945602416992</v>
+        <v>43.64945220947266</v>
       </c>
       <c r="C171" t="n">
         <v>53.4900016784668</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>36.42601776123047</v>
+        <v>36.42602157592773</v>
       </c>
       <c r="C172" t="n">
         <v>44.25</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>37.77604293823242</v>
+        <v>37.77605056762695</v>
       </c>
       <c r="C173" t="n">
         <v>45.88999938964844</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>38.42635726928711</v>
+        <v>38.42635345458984</v>
       </c>
       <c r="C174" t="n">
         <v>46.68000030517578</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>37.11413192749023</v>
+        <v>37.1141242980957</v>
       </c>
       <c r="C175" t="n">
         <v>44.68000030517578</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>39.24063491821289</v>
+        <v>39.24063110351562</v>
       </c>
       <c r="C176" t="n">
         <v>47.2400016784668</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>41.14286041259766</v>
+        <v>41.14285278320312</v>
       </c>
       <c r="C177" t="n">
         <v>49.52999877929688</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>40.24493026733398</v>
+        <v>40.24493789672852</v>
       </c>
       <c r="C179" t="n">
         <v>48.06000137329102</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>43.548095703125</v>
+        <v>43.54809188842773</v>
       </c>
       <c r="C180" t="n">
         <v>51.59999847412109</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>46.28250503540039</v>
+        <v>46.28250885009766</v>
       </c>
       <c r="C181" t="n">
         <v>54.84000015258789</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>40.63644409179688</v>
+        <v>40.63644790649414</v>
       </c>
       <c r="C182" t="n">
         <v>48.15000152587891</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>44.85515213012695</v>
+        <v>44.85514450073242</v>
       </c>
       <c r="C184" t="n">
         <v>52.70999908447266</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>47.0506706237793</v>
+        <v>47.05067443847656</v>
       </c>
       <c r="C186" t="n">
         <v>55.29000091552734</v>
@@ -5367,7 +5367,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>46.39348220825195</v>
+        <v>46.39348602294922</v>
       </c>
       <c r="C187" t="n">
         <v>54.11000061035156</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>48.69594192504883</v>
+        <v>48.69594573974609</v>
       </c>
       <c r="C191" t="n">
         <v>56.36999893188477</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>45.66097640991211</v>
+        <v>45.66096878051758</v>
       </c>
       <c r="C192" t="n">
         <v>52.45000076293945</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>53.11297988891602</v>
+        <v>53.11299133300781</v>
       </c>
       <c r="C194" t="n">
         <v>61.0099983215332</v>
@@ -5599,7 +5599,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>54.18377685546875</v>
+        <v>54.18378067016602</v>
       </c>
       <c r="C195" t="n">
         <v>62.2400016784668</v>
@@ -5715,7 +5715,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>55.58500671386719</v>
+        <v>55.58500289916992</v>
       </c>
       <c r="C199" t="n">
         <v>62.90999984741211</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>49.85812759399414</v>
+        <v>49.85812377929688</v>
       </c>
       <c r="C202" t="n">
         <v>56.02000045776367</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>53.266845703125</v>
+        <v>53.26684188842773</v>
       </c>
       <c r="C203" t="n">
         <v>59.84999847412109</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>54.96220397949219</v>
+        <v>54.96221542358398</v>
       </c>
       <c r="C206" t="n">
         <v>61.31999969482422</v>
@@ -5947,7 +5947,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>53.33987808227539</v>
+        <v>53.33987426757812</v>
       </c>
       <c r="C207" t="n">
         <v>59.5099983215332</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>56.02506256103516</v>
+        <v>56.02506637573242</v>
       </c>
       <c r="C208" t="n">
         <v>62.02999877929688</v>
@@ -6005,7 +6005,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>57.93983459472656</v>
+        <v>57.9398307800293</v>
       </c>
       <c r="C209" t="n">
         <v>64.15000152587891</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>53.88449478149414</v>
+        <v>53.88449859619141</v>
       </c>
       <c r="C210" t="n">
         <v>59.65999984741211</v>
@@ -6092,7 +6092,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>56.36073684692383</v>
+        <v>56.36074066162109</v>
       </c>
       <c r="C212" t="n">
         <v>61.93000030517578</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>51.81782150268555</v>
+        <v>51.81782913208008</v>
       </c>
       <c r="C215" t="n">
         <v>56.4900016784668</v>
@@ -6208,7 +6208,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>54.03338623046875</v>
+        <v>54.03339767456055</v>
       </c>
       <c r="C216" t="n">
         <v>58.43999862670898</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>54.4864387512207</v>
+        <v>54.48644256591797</v>
       </c>
       <c r="C217" t="n">
         <v>58.93000030517578</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>55.00422286987305</v>
+        <v>55.00421905517578</v>
       </c>
       <c r="C218" t="n">
         <v>59.4900016784668</v>
@@ -6295,7 +6295,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>55.4942512512207</v>
+        <v>55.49425506591797</v>
       </c>
       <c r="C219" t="n">
         <v>60.02000045776367</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>57.56912231445312</v>
+        <v>57.56911849975586</v>
       </c>
       <c r="C221" t="n">
         <v>61.77000045776367</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>58.65023422241211</v>
+        <v>58.65023040771484</v>
       </c>
       <c r="C222" t="n">
         <v>62.93000030517578</v>
@@ -6411,7 +6411,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>59.78156280517578</v>
+        <v>59.78155899047852</v>
       </c>
       <c r="C223" t="n">
         <v>63.65000152587891</v>
@@ -6440,7 +6440,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>62.68375015258789</v>
+        <v>62.68376159667969</v>
       </c>
       <c r="C224" t="n">
         <v>66.73999786376953</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>67.95528411865234</v>
+        <v>67.95527648925781</v>
       </c>
       <c r="C226" t="n">
         <v>71.86000061035156</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>61.05764389038086</v>
+        <v>61.05764770507812</v>
       </c>
       <c r="C228" t="n">
         <v>64.08000183105469</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>67.85136413574219</v>
+        <v>67.85135650634766</v>
       </c>
       <c r="C231" t="n">
         <v>71.20999908447266</v>
@@ -6759,7 +6759,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>68.39337158203125</v>
+        <v>68.39337921142578</v>
       </c>
       <c r="C235" t="n">
         <v>70.75</v>
@@ -6788,7 +6788,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>65.62863159179688</v>
+        <v>65.62863922119141</v>
       </c>
       <c r="C236" t="n">
         <v>67.88999938964844</v>
@@ -6817,7 +6817,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>66.69199371337891</v>
+        <v>66.69198608398438</v>
       </c>
       <c r="C237" t="n">
         <v>68.98999786376953</v>
@@ -6875,7 +6875,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>67.11579895019531</v>
+        <v>67.11580657958984</v>
       </c>
       <c r="C239" t="n">
         <v>68.90000152587891</v>
